--- a/server/excel/release/substitute-hero.xlsx
+++ b/server/excel/release/substitute-hero.xlsx
@@ -1,137 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26625" windowHeight="13140"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="替补英雄基础" sheetId="1" r:id="rId1"/>
+    <sheet name="替补英雄基础" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>英雄星级</t>
-  </si>
-  <si>
-    <t>属性增加</t>
-  </si>
-  <si>
-    <t>buffId</t>
-  </si>
-  <si>
-    <t>BUFF描述</t>
-  </si>
-  <si>
-    <t>1001:100#1004:100</t>
-  </si>
-  <si>
-    <t>1001:200#1004:200</t>
-  </si>
-  <si>
-    <t>1001:300#1004:300</t>
-  </si>
-  <si>
-    <t>1001:400#1004:400</t>
-  </si>
-  <si>
-    <t>1001:500#1004:500</t>
-  </si>
-  <si>
-    <t>1001:600#1004:600</t>
-  </si>
-  <si>
-    <t>4051#4070</t>
-  </si>
-  <si>
-    <t>1001:700#1004:700</t>
-  </si>
-  <si>
-    <t>4052#4071</t>
-  </si>
-  <si>
-    <t>1001:800#1004:800</t>
-  </si>
-  <si>
-    <t>4053#4072</t>
-  </si>
-  <si>
-    <t>1001:900#1004:900</t>
-  </si>
-  <si>
-    <t>4054#4073</t>
-  </si>
-  <si>
-    <t>1001:1000#1004:1000</t>
-  </si>
-  <si>
-    <t>4055#4074</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 5%, tiếp tục 3 Hiệp</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 7%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 5% HP</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 9%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 5% HP</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 11%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 10% HP</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 13%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 10% HP</t>
-  </si>
-  <si>
-    <t>Chi viện anh hùng ra trận lúc, toàn đội thụ liệu gia tăng 15%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 15% HP</t>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄星级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属性增加</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buffId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUFF描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:100#1004:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:200#1004:200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:300#1004:300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:400#1004:400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:500#1004:500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 5%, tiếp tục 3 Hiệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:600#1004:600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4051#4070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 7%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 5% HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:700#1004:700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4052#4071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 9%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 5% HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:800#1004:800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4053#4072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 11%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 10% HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:900#1004:900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4054#4073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 13%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 10% HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001:1000#1004:1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4055#4074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi viện tướng ra trận lúc, toàn đội thụ liệu gia tăng 15%, tiếp tục 3 Hiệp, đồng thời khôi phục toàn đội sinh mệnh hạn mức cao nhất 15% HP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79946287423322249"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -144,39 +127,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -250,7 +282,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -285,7 +316,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -461,18 +491,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="74.85546875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,170 +516,169 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+      <c r="D4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
+      <c r="D5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>4050</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B11" t="n">
         <v>14</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D11" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="D15" s="2"/>
+    <row r="12">
+      <c r="D12"/>
+    </row>
+    <row r="13">
+      <c r="D13"/>
+    </row>
+    <row r="14">
+      <c r="D14"/>
+    </row>
+    <row r="15">
+      <c r="D15"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>